--- a/exports/AMBER_full_report.xlsx
+++ b/exports/AMBER_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:U67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>8.17</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>3450</v>
+        <v>3238.5</v>
       </c>
       <c r="I2" t="n">
         <v>3345.906741373174</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.33</v>
+        <v>-7.38</v>
       </c>
       <c r="L2" t="n">
-        <v>3.51</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="N2" t="n">
-        <v>3.77</v>
+        <v>7.68</v>
       </c>
       <c r="O2" t="n">
         <v>1.16</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>12.63</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44589.55208333334</v>
+        <v>44592.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>3150.1</v>
+        <v>3511.8</v>
       </c>
       <c r="I3" t="n">
         <v>3389.031344853584</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>2.73</v>
+        <v>-8.44</v>
       </c>
       <c r="L3" t="n">
-        <v>5.32</v>
+        <v>10.55</v>
       </c>
       <c r="M3" t="n">
-        <v>0.16</v>
+        <v>4.76</v>
       </c>
       <c r="N3" t="n">
-        <v>1.78</v>
+        <v>14.97</v>
       </c>
       <c r="O3" t="n">
         <v>-7.68</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>16</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44600.38541666666</v>
+        <v>44600.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>3452</v>
+        <v>3428.9</v>
       </c>
       <c r="I4" t="n">
         <v>3430.23605420948</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.7</v>
+        <v>-2.36</v>
       </c>
       <c r="L4" t="n">
         <v>10.12</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.91</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44620.38541666666</v>
+        <v>44620.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>3351</v>
+        <v>3465</v>
       </c>
       <c r="I5" t="n">
         <v>3421.630539425635</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>2.27</v>
+        <v>-1.05</v>
       </c>
       <c r="L5" t="n">
         <v>5.36</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>11.7</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44690.38541666666</v>
+        <v>44690.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>3602.35</v>
+        <v>3571.55</v>
       </c>
       <c r="I6" t="n">
         <v>3579.993287043671</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>69.83333333333333</v>
+        <v>70</v>
       </c>
       <c r="K6" t="n">
-        <v>3.96</v>
+        <v>3.08</v>
       </c>
       <c r="L6" t="n">
         <v>3.67</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.93</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44740.55208333334</v>
+        <v>44741.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>2292</v>
+        <v>2376.05</v>
       </c>
       <c r="I7" t="n">
         <v>2297.839653022742</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>50</v>
+        <v>50.83333333333334</v>
       </c>
       <c r="K7" t="n">
-        <v>35.83</v>
+        <v>33.47</v>
       </c>
       <c r="L7" t="n">
         <v>3.16</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>10.43</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44777.55208333334</v>
+        <v>44778.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>2384</v>
+        <v>2290.65</v>
       </c>
       <c r="I8" t="n">
         <v>2351.519812544393</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K8" t="n">
-        <v>0.33</v>
+        <v>-3.59</v>
       </c>
       <c r="L8" t="n">
         <v>6.69</v>
@@ -897,7 +992,7 @@
         <v>1.4</v>
       </c>
       <c r="N8" t="n">
-        <v>4.35</v>
+        <v>4.99</v>
       </c>
       <c r="O8" t="n">
         <v>2.09</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>11.25</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44816.55208333334</v>
+        <v>44817.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>2319</v>
+        <v>2371.45</v>
       </c>
       <c r="I9" t="n">
         <v>2353.861299002043</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.24</v>
+        <v>-3.53</v>
       </c>
       <c r="L9" t="n">
         <v>4.64</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>5.47</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44820.55208333334</v>
+        <v>44823.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>2293.4</v>
+        <v>2233.1</v>
       </c>
       <c r="I10" t="n">
         <v>2241.689574434087</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.29</v>
+        <v>-5.83</v>
       </c>
       <c r="L10" t="n">
-        <v>5.06</v>
+        <v>6.39</v>
       </c>
       <c r="M10" t="n">
         <v>0.73</v>
       </c>
       <c r="N10" t="n">
-        <v>2.49</v>
+        <v>2.77</v>
       </c>
       <c r="O10" t="n">
         <v>0.04</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>7.21</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44833.38541666666</v>
+        <v>44833.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>2244.8</v>
+        <v>2305</v>
       </c>
       <c r="I11" t="n">
         <v>2297.559294516551</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.52</v>
+        <v>-3.22</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="M11" t="n">
         <v>1.18</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>8.15</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44848.55208333334</v>
+        <v>44851.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>2243</v>
+        <v>2222.05</v>
       </c>
       <c r="I12" t="n">
         <v>2242.01318832099</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>15</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.69</v>
+        <v>-3.6</v>
       </c>
       <c r="L12" t="n">
-        <v>3.55</v>
+        <v>4.01</v>
       </c>
       <c r="M12" t="n">
         <v>0.86</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>6.53</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44896.55208333334</v>
+        <v>44897.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>1939.95</v>
+        <v>2033.7</v>
       </c>
       <c r="I13" t="n">
         <v>2017.592711212182</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K13" t="n">
-        <v>12.7</v>
+        <v>8.48</v>
       </c>
       <c r="L13" t="n">
         <v>3.03</v>
@@ -1182,7 +1337,7 @@
         <v>1.77</v>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>3.61</v>
       </c>
       <c r="O13" t="n">
         <v>-0.74</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>6.95</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44916.55208333334</v>
+        <v>44917.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>1939.9</v>
+        <v>1928.2</v>
       </c>
       <c r="I14" t="n">
         <v>1930.896162279634</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.61</v>
+        <v>-5.19</v>
       </c>
       <c r="L14" t="n">
         <v>5.48</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>4.67</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44945.55208333334</v>
+        <v>44946.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>1873.55</v>
+        <v>1929.6</v>
       </c>
       <c r="I15" t="n">
         <v>1926.717360351945</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K15" t="n">
-        <v>2.83</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L15" t="n">
         <v>2.12</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>5.75</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44958.38541666666</v>
+        <v>44958.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>1900.25</v>
+        <v>1877.1</v>
       </c>
       <c r="I16" t="n">
         <v>1894.443034479234</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.52</v>
+        <v>-2.72</v>
       </c>
       <c r="L16" t="n">
-        <v>2.97</v>
+        <v>3.71</v>
       </c>
       <c r="M16" t="n">
         <v>1.25</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44987.38541666666</v>
+        <v>44987.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>1919</v>
+        <v>1946.9</v>
       </c>
       <c r="I17" t="n">
         <v>1937.440654860294</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>28.83333333333333</v>
+        <v>29</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.23</v>
+        <v>-3.72</v>
       </c>
       <c r="L17" t="n">
-        <v>3.64</v>
+        <v>4.42</v>
       </c>
       <c r="M17" t="n">
         <v>0.88</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.26</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45001.55208333334</v>
+        <v>45002.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>1930</v>
+        <v>1914.9</v>
       </c>
       <c r="I18" t="n">
         <v>1919.347281375615</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.87</v>
+        <v>-1.64</v>
       </c>
       <c r="L18" t="n">
         <v>2.66</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>6.64</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45061.55208333334</v>
+        <v>45062.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>1840.05</v>
+        <v>1939.45</v>
       </c>
       <c r="I19" t="n">
         <v>1877.222293199581</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>59.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K19" t="n">
-        <v>3.91</v>
+        <v>-1.28</v>
       </c>
       <c r="L19" t="n">
         <v>2.62</v>
@@ -1524,7 +1751,7 @@
         <v>1.72</v>
       </c>
       <c r="N19" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="O19" t="n">
         <v>-0.52</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.74</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45181.55208333334</v>
+        <v>45182.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>2880</v>
+        <v>2849.45</v>
       </c>
       <c r="I20" t="n">
         <v>2867.906580310773</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>119.1666666666667</v>
+        <v>120</v>
       </c>
       <c r="K20" t="n">
-        <v>48.5</v>
+        <v>46.92</v>
       </c>
       <c r="L20" t="n">
         <v>4.35</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>168</v>
+        <v>169</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>8.01</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45195.55208333334</v>
+        <v>45196.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>2991.35</v>
+        <v>3055</v>
       </c>
       <c r="I21" t="n">
         <v>3041.196348217083</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.98</v>
+        <v>-7.21</v>
       </c>
       <c r="L21" t="n">
-        <v>6.44</v>
+        <v>7.42</v>
       </c>
       <c r="M21" t="n">
         <v>1.56</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>7.38</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45205.55208333334</v>
+        <v>45208.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>2920</v>
+        <v>2831.2</v>
       </c>
       <c r="I22" t="n">
         <v>2878.089788944608</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.42</v>
+        <v>-7.33</v>
       </c>
       <c r="L22" t="n">
-        <v>6.46</v>
+        <v>7.84</v>
       </c>
       <c r="M22" t="n">
         <v>0.37</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45218.55208333334</v>
+        <v>45219.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>2959</v>
+        <v>3053</v>
       </c>
       <c r="I23" t="n">
         <v>3019.300635539083</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.51</v>
+        <v>-7.83</v>
       </c>
       <c r="L23" t="n">
-        <v>7.42</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="M23" t="n">
         <v>0.67</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>7.26</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>3035</v>
+        <v>2805.85</v>
       </c>
       <c r="I24" t="n">
         <v>2859.104575548092</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.59</v>
+        <v>-8.1</v>
       </c>
       <c r="L24" t="n">
-        <v>3.08</v>
+        <v>10.87</v>
       </c>
       <c r="M24" t="n">
-        <v>-0</v>
+        <v>4.78</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>8.57</v>
       </c>
       <c r="O24" t="n">
         <v>2.57</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>9.43</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45233.38541666666</v>
+        <v>45233.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>3016</v>
+        <v>3130</v>
       </c>
       <c r="I25" t="n">
         <v>3031.340043806046</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-7.49</v>
+        <v>-11.55</v>
       </c>
       <c r="L25" t="n">
-        <v>7.88</v>
+        <v>12.44</v>
       </c>
       <c r="M25" t="n">
         <v>4.34</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>9.15</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45239.55208333334</v>
+        <v>45240.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>3136</v>
+        <v>3037</v>
       </c>
       <c r="I26" t="n">
         <v>3119.831247479368</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>0.19</v>
+        <v>-2.97</v>
       </c>
       <c r="L26" t="n">
-        <v>3.67</v>
+        <v>5.09</v>
       </c>
       <c r="M26" t="n">
         <v>1.47</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>11.52</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45247.55208333334</v>
+        <v>45250.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>3200</v>
+        <v>3412.85</v>
       </c>
       <c r="I27" t="n">
         <v>3356.378285675908</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.37</v>
+        <v>-12.38</v>
       </c>
       <c r="L27" t="n">
-        <v>8.59</v>
+        <v>12.61</v>
       </c>
       <c r="M27" t="n">
         <v>2.65</v>
       </c>
       <c r="N27" t="n">
-        <v>3.96</v>
+        <v>4.59</v>
       </c>
       <c r="O27" t="n">
         <v>-2.61</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>12.35</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45258.55208333334</v>
+        <v>45259.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>3139.9</v>
+        <v>3070</v>
       </c>
       <c r="I28" t="n">
         <v>3092.473275728021</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K28" t="n">
-        <v>-8</v>
+        <v>-10.05</v>
       </c>
       <c r="L28" t="n">
-        <v>8.43</v>
+        <v>10.16</v>
       </c>
       <c r="M28" t="n">
         <v>0.27</v>
       </c>
       <c r="N28" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="O28" t="n">
         <v>4.59</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>10.6</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45274.55208333334</v>
+        <v>45275.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>3138.45</v>
+        <v>3339.95</v>
       </c>
       <c r="I29" t="n">
         <v>3253.795718239016</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.23</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>4.73</v>
+        <v>10.36</v>
       </c>
       <c r="M29" t="n">
         <v>2.43</v>
       </c>
       <c r="N29" t="n">
-        <v>2.56</v>
+        <v>5.79</v>
       </c>
       <c r="O29" t="n">
         <v>-3.18</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>9.32</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>3137.1</v>
+        <v>3062</v>
       </c>
       <c r="I30" t="n">
         <v>3086.363059263382</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>-6.07</v>
+        <v>-8.32</v>
       </c>
       <c r="L30" t="n">
-        <v>6.47</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="M30" t="n">
         <v>0.03</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45295.55208333334</v>
+        <v>45296.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>3193</v>
+        <v>3275.1</v>
       </c>
       <c r="I31" t="n">
         <v>3230.864407677108</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.28</v>
+        <v>-6.96</v>
       </c>
       <c r="L31" t="n">
-        <v>5.75</v>
+        <v>7.58</v>
       </c>
       <c r="M31" t="n">
         <v>1.43</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>5.99</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45331.55208333334</v>
+        <v>45334.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>4088</v>
+        <v>3618.05</v>
       </c>
       <c r="I32" t="n">
         <v>3996.510546486759</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K32" t="n">
-        <v>24.82</v>
+        <v>10.47</v>
       </c>
       <c r="L32" t="n">
         <v>1.98</v>
       </c>
       <c r="M32" t="n">
-        <v>2.07</v>
+        <v>9.49</v>
       </c>
       <c r="N32" t="n">
-        <v>4.64</v>
+        <v>9.52</v>
       </c>
       <c r="O32" t="n">
         <v>2</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>20.08</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45372.55208333334</v>
+        <v>45373.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>3385</v>
+        <v>3561.15</v>
       </c>
       <c r="I33" t="n">
         <v>3520.980428698975</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K33" t="n">
-        <v>6.44</v>
+        <v>1.57</v>
       </c>
       <c r="L33" t="n">
         <v>14.65</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>13.26</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45421.55208333334</v>
+        <v>45422.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>3875</v>
+        <v>3794.9</v>
       </c>
       <c r="I34" t="n">
         <v>3819.762676097856</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K34" t="n">
-        <v>8.81</v>
+        <v>6.56</v>
       </c>
       <c r="L34" t="n">
         <v>3.46</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>10.3</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45449.55208333334</v>
+        <v>45450.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>3715</v>
+        <v>3776.8</v>
       </c>
       <c r="I35" t="n">
         <v>3767.338218649686</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K35" t="n">
-        <v>2.11</v>
+        <v>0.48</v>
       </c>
       <c r="L35" t="n">
         <v>8.039999999999999</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.13</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45489.55208333334</v>
+        <v>45491.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>4552.1</v>
+        <v>4384</v>
       </c>
       <c r="I36" t="n">
         <v>4394.9941409889</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K36" t="n">
-        <v>20.53</v>
+        <v>16.08</v>
       </c>
       <c r="L36" t="n">
         <v>1.74</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>9.94</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45531.55208333334</v>
+        <v>45532.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>4304.9</v>
+        <v>4381.65</v>
       </c>
       <c r="I37" t="n">
         <v>4331.80133688583</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K37" t="n">
-        <v>1.8</v>
+        <v>0.05</v>
       </c>
       <c r="L37" t="n">
         <v>5.27</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>6.23</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45553.55208333334</v>
+        <v>45554.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>4444</v>
+        <v>4294.55</v>
       </c>
       <c r="I38" t="n">
         <v>4370.514400618817</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K38" t="n">
-        <v>1.42</v>
+        <v>-1.99</v>
       </c>
       <c r="L38" t="n">
-        <v>1.62</v>
+        <v>2.64</v>
       </c>
       <c r="M38" t="n">
         <v>1.01</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45555.55208333334</v>
+        <v>45558.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>4346.8</v>
+        <v>4869.7</v>
       </c>
       <c r="I39" t="n">
         <v>4647.057694353407</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.22</v>
+        <v>-13.39</v>
       </c>
       <c r="L39" t="n">
-        <v>4.55</v>
+        <v>13.75</v>
       </c>
       <c r="M39" t="n">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>13.28</v>
       </c>
       <c r="O39" t="n">
         <v>-1.49</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>13.58</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45630.55208333334</v>
+        <v>45631.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>6010</v>
+        <v>5892.55</v>
       </c>
       <c r="I40" t="n">
         <v>5980.580582778873</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>72.16666666666667</v>
+        <v>73</v>
       </c>
       <c r="K40" t="n">
-        <v>23.42</v>
+        <v>21</v>
       </c>
       <c r="L40" t="n">
         <v>10.01</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45642.55208333334</v>
+        <v>45643.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>5980</v>
+        <v>6046.55</v>
       </c>
       <c r="I41" t="n">
         <v>6039.318448997333</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.48</v>
+        <v>-2.61</v>
       </c>
       <c r="L41" t="n">
-        <v>3.62</v>
+        <v>4.27</v>
       </c>
       <c r="M41" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.67</v>
       </c>
       <c r="N41" t="n">
         <v>3.15</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.02</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45670.38541666666</v>
+        <v>45670.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>7322.1</v>
+        <v>7089.7</v>
       </c>
       <c r="I42" t="n">
         <v>7249.847817630944</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K42" t="n">
-        <v>21.1</v>
+        <v>17.25</v>
       </c>
       <c r="L42" t="n">
         <v>2.84</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>15.16</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45722.55208333334</v>
+        <v>45723.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>6165</v>
+        <v>6345</v>
       </c>
       <c r="I43" t="n">
         <v>6265.378194733974</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>52</v>
+        <v>52.83333333333334</v>
       </c>
       <c r="K43" t="n">
-        <v>13.04</v>
+        <v>10.5</v>
       </c>
       <c r="L43" t="n">
         <v>4.07</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>11.07</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45750.55208333334</v>
+        <v>45751.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>6935</v>
+        <v>6625</v>
       </c>
       <c r="I44" t="n">
         <v>6665.639480276887</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K44" t="n">
-        <v>9.300000000000001</v>
+        <v>4.41</v>
       </c>
       <c r="L44" t="n">
         <v>2.91</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>11.38</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>6500</v>
+        <v>6881.5</v>
       </c>
       <c r="I45" t="n">
         <v>6779.972608225954</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>11</v>
       </c>
       <c r="K45" t="n">
-        <v>1.89</v>
+        <v>-3.87</v>
       </c>
       <c r="L45" t="n">
         <v>5.26</v>
@@ -3006,7 +3545,7 @@
         <v>4.88</v>
       </c>
       <c r="N45" t="n">
-        <v>5.4</v>
+        <v>5.83</v>
       </c>
       <c r="O45" t="n">
         <v>-4.43</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>11.77</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45777.38541666666</v>
+        <v>45777.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>6261.5</v>
+        <v>6090</v>
       </c>
       <c r="I46" t="n">
         <v>6218.736354332774</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K46" t="n">
-        <v>-9.01</v>
+        <v>-11.5</v>
       </c>
       <c r="L46" t="n">
-        <v>10.14</v>
+        <v>12.01</v>
       </c>
       <c r="M46" t="n">
         <v>0.39</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>8.9</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45791.55208333334</v>
+        <v>45792.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>6312</v>
+        <v>6340.5</v>
       </c>
       <c r="I47" t="n">
         <v>6331.84720462912</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.65</v>
+        <v>-4.11</v>
       </c>
       <c r="L47" t="n">
         <v>5.41</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.38</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45860.55208333334</v>
+        <v>45861.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>7383.5</v>
+        <v>7310.5</v>
       </c>
       <c r="I48" t="n">
         <v>7332.911505491984</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>68.16666666666667</v>
+        <v>69</v>
       </c>
       <c r="K48" t="n">
-        <v>16.45</v>
+        <v>15.3</v>
       </c>
       <c r="L48" t="n">
         <v>2.18</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>6.51</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45867.38541666666</v>
+        <v>45867.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>7649.5</v>
+        <v>7833</v>
       </c>
       <c r="I49" t="n">
         <v>7662.536785828985</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.64</v>
+        <v>-7.15</v>
       </c>
       <c r="L49" t="n">
-        <v>4.64</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="M49" t="n">
         <v>0.3</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>8.91</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45877.38541666666</v>
+        <v>45877.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>7613.5</v>
+        <v>7300</v>
       </c>
       <c r="I50" t="n">
         <v>7424.292061655897</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.8</v>
+        <v>-6.8</v>
       </c>
       <c r="L50" t="n">
-        <v>4.68</v>
+        <v>7.08</v>
       </c>
       <c r="M50" t="n">
         <v>1.55</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>10.28</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45883.55208333334</v>
+        <v>45887.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>6885.5</v>
+        <v>7420</v>
       </c>
       <c r="I51" t="n">
         <v>7401.377899927966</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>6</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K51" t="n">
-        <v>5.68</v>
+        <v>-1.64</v>
       </c>
       <c r="L51" t="n">
         <v>4.51</v>
       </c>
       <c r="M51" t="n">
-        <v>0.65</v>
+        <v>4.68</v>
       </c>
       <c r="N51" t="n">
-        <v>1.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O51" t="n">
         <v>-6.11</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>9.69</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45960.55208333334</v>
+        <v>45961.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>8118</v>
+        <v>8057</v>
       </c>
       <c r="I52" t="n">
         <v>8101.847707705991</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>73.16666666666667</v>
+        <v>74</v>
       </c>
       <c r="K52" t="n">
-        <v>9.41</v>
+        <v>8.58</v>
       </c>
       <c r="L52" t="n">
         <v>3.36</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.23</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46024.55208333334</v>
+        <v>46027.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>6479.5</v>
+        <v>6738.5</v>
       </c>
       <c r="I53" t="n">
         <v>6639.014609783067</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>66</v>
       </c>
       <c r="K53" t="n">
-        <v>19.58</v>
+        <v>16.36</v>
       </c>
       <c r="L53" t="n">
         <v>1.48</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>6.73</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46031.38541666666</v>
+        <v>46031.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>6370</v>
+        <v>6337</v>
       </c>
       <c r="I54" t="n">
         <v>6348.743493409944</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-5.47</v>
+        <v>-5.96</v>
       </c>
       <c r="L54" t="n">
-        <v>5.52</v>
+        <v>6.35</v>
       </c>
       <c r="M54" t="n">
         <v>0.28</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>5.78</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46052.55208333334</v>
+        <v>46054.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>5731</v>
+        <v>5944</v>
       </c>
       <c r="I55" t="n">
         <v>5875.181858588787</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>21</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>9.56</v>
+        <v>6.2</v>
       </c>
       <c r="L55" t="n">
         <v>0.76</v>
@@ -3576,7 +4235,7 @@
         <v>1.14</v>
       </c>
       <c r="N55" t="n">
-        <v>3.17</v>
+        <v>4.66</v>
       </c>
       <c r="O55" t="n">
         <v>-2.78</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>8.85</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>7890</v>
+        <v>7586.5</v>
       </c>
       <c r="I56" t="n">
         <v>7627.221103927228</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K56" t="n">
-        <v>32.74</v>
+        <v>27.63</v>
       </c>
       <c r="L56" t="n">
         <v>3.84</v>
@@ -3633,7 +4304,7 @@
         <v>4.47</v>
       </c>
       <c r="N56" t="n">
-        <v>2.35</v>
+        <v>3.07</v>
       </c>
       <c r="O56" t="n">
         <v>4.66</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>7.77</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>6436</v>
+        <v>6968.5</v>
       </c>
       <c r="I57" t="n">
         <v>6866.41335056204</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K57" t="n">
-        <v>15.17</v>
+        <v>8.15</v>
       </c>
       <c r="L57" t="n">
         <v>4.73</v>
       </c>
       <c r="M57" t="n">
-        <v>3.75</v>
+        <v>4.02</v>
       </c>
       <c r="N57" t="n">
-        <v>4.95</v>
+        <v>7.83</v>
       </c>
       <c r="O57" t="n">
         <v>-3.07</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>11.42</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46154.38541666666</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>8281.5</v>
+        <v>8200</v>
       </c>
       <c r="I58" t="n">
         <v>8266.641786139078</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K58" t="n">
-        <v>18.84</v>
+        <v>17.67</v>
       </c>
       <c r="L58" t="n">
         <v>4.44</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.44</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46178.38541666666</v>
+        <v>46178.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>7750</v>
+        <v>7884</v>
       </c>
       <c r="I59" t="n">
         <v>7841.737429384261</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>23.83333333333333</v>
+        <v>24</v>
       </c>
       <c r="K59" t="n">
-        <v>5.49</v>
+        <v>3.85</v>
       </c>
       <c r="L59" t="n">
         <v>4.16</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46202.38541666666</v>
+        <v>46202.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>7451.5</v>
+        <v>7433</v>
       </c>
       <c r="I60" t="n">
         <v>7448.716672956278</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>23.83333333333333</v>
+        <v>24</v>
       </c>
       <c r="K60" t="n">
-        <v>-5.49</v>
+        <v>-5.72</v>
       </c>
       <c r="L60" t="n">
         <v>9.69</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>7.67</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46218.38541666666</v>
+        <v>46218.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>7832</v>
+        <v>7881.5</v>
       </c>
       <c r="I61" t="n">
         <v>7838.12193253913</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>15.83333333333333</v>
+        <v>16</v>
       </c>
       <c r="K61" t="n">
-        <v>-5.37</v>
+        <v>-6.03</v>
       </c>
       <c r="L61" t="n">
         <v>7.02</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>5.92</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46225.38541666666</v>
+        <v>46225.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>7552</v>
+        <v>7480</v>
       </c>
       <c r="I62" t="n">
         <v>7549.131342649111</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.18</v>
+        <v>-5.09</v>
       </c>
       <c r="L62" t="n">
-        <v>4.54</v>
+        <v>5.61</v>
       </c>
       <c r="M62" t="n">
         <v>0.18</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.36</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46255.55208333334</v>
+        <v>46258.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>7353</v>
+        <v>7367</v>
       </c>
       <c r="I63" t="n">
         <v>7364.03297392259</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>30</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K63" t="n">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="L63" t="n">
         <v>1.16</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>4.62</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46266.55208333334</v>
+        <v>46267.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>7500</v>
+        <v>7361</v>
       </c>
       <c r="I64" t="n">
         <v>7381.407333896424</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K64" t="n">
-        <v>1.81</v>
+        <v>-0.08</v>
       </c>
       <c r="L64" t="n">
         <v>1.18</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>5.07</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46301.38541666666</v>
+        <v>46301.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>6771</v>
+        <v>6860</v>
       </c>
       <c r="I65" t="n">
         <v>6857.634900295044</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K65" t="n">
-        <v>8.02</v>
+        <v>6.81</v>
       </c>
       <c r="L65" t="n">
         <v>2.21</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>6.61</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46303.55208333334</v>
+        <v>46304.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>6560</v>
+        <v>6448</v>
       </c>
       <c r="I66" t="n">
         <v>6456.592657952301</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K66" t="n">
-        <v>-4.37</v>
+        <v>-6.01</v>
       </c>
       <c r="L66" t="n">
-        <v>4.52</v>
+        <v>7</v>
       </c>
       <c r="M66" t="n">
         <v>0.73</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4263,6 +5066,12 @@
       <c r="Q67" t="n">
         <v>24</v>
       </c>
+      <c r="R67" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6365,7 +7174,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.5</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="6">
@@ -6375,7 +7184,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -6385,7 +7194,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>119.2</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8">
@@ -6395,7 +7204,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -6405,7 +7214,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.2</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -6415,7 +7224,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>56.3</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="11">
@@ -6425,7 +7234,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
@@ -6435,7 +7244,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -6445,7 +7254,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69.2</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="14">
@@ -6455,7 +7264,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -6465,7 +7274,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.31</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="16">
@@ -6475,7 +7284,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.17</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="17">
@@ -6485,7 +7294,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>48.5</v>
+        <v>46.92</v>
       </c>
     </row>
     <row r="18">
@@ -6495,7 +7304,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.3</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="19">
@@ -6505,7 +7314,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.77</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="20">
@@ -6515,7 +7324,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.51</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="21">
@@ -6535,7 +7344,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
@@ -6545,7 +7354,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -6555,7 +7364,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="25">
@@ -6565,7 +7374,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.67</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="26">
@@ -6575,7 +7384,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.11</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="27">
@@ -6585,7 +7394,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.99</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="28">
@@ -6595,7 +7404,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29">
